--- a/app/features/process_shipment/filleo/templates/formato-envio.xlsx
+++ b/app/features/process_shipment/filleo/templates/formato-envio.xlsx
@@ -542,7 +542,7 @@
       </c>
       <c r="G2" s="2" t="inlineStr">
         <is>
-          <t>ICA SAN JOAQUIN</t>
+          <t>CAJAMARCA CO</t>
         </is>
       </c>
       <c r="H2" s="2" t="inlineStr">
